--- a/artfynd/A 22724-2025 artfynd.xlsx
+++ b/artfynd/A 22724-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136304584</v>
       </c>
       <c r="B2" t="n">
-        <v>93387</v>
+        <v>93388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136304592</v>
       </c>
       <c r="B3" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22724-2025 artfynd.xlsx
+++ b/artfynd/A 22724-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136304584</v>
       </c>
       <c r="B2" t="n">
-        <v>93388</v>
+        <v>93394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136304592</v>
       </c>
       <c r="B3" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22724-2025 artfynd.xlsx
+++ b/artfynd/A 22724-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136304584</v>
       </c>
       <c r="B2" t="n">
-        <v>93394</v>
+        <v>93401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136304592</v>
       </c>
       <c r="B3" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22724-2025 artfynd.xlsx
+++ b/artfynd/A 22724-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136304584</v>
       </c>
       <c r="B2" t="n">
-        <v>93401</v>
+        <v>93402</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136304592</v>
       </c>
       <c r="B3" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22724-2025 artfynd.xlsx
+++ b/artfynd/A 22724-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136304584</v>
       </c>
       <c r="B2" t="n">
-        <v>93402</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136304592</v>
       </c>
       <c r="B3" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22724-2025 artfynd.xlsx
+++ b/artfynd/A 22724-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136304584</v>
       </c>
       <c r="B2" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136304592</v>
       </c>
       <c r="B3" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
